--- a/exports/INDIANB_full_report.xlsx
+++ b/exports/INDIANB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>133.5</v>
+        <v>128.2</v>
       </c>
       <c r="I2" t="n">
         <v>133.3020822703106</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.72</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>6.53</v>
+        <v>9.92</v>
       </c>
       <c r="M2" t="n">
         <v>0.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2.69</v>
+        <v>4.87</v>
       </c>
       <c r="O2" t="n">
         <v>3.27</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.38541666666</v>
+        <v>44588.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>135.05</v>
+        <v>139.15</v>
       </c>
       <c r="I3" t="n">
         <v>136.6628766557026</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.34</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>5.54</v>
+        <v>9.4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44600.55208333334</v>
+        <v>44601.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>149</v>
+        <v>147.6</v>
       </c>
       <c r="I4" t="n">
         <v>147.6321590517556</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>7.08</v>
+        <v>6.07</v>
       </c>
       <c r="L4" t="n">
         <v>3.02</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.61</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.38541666666</v>
+        <v>44628.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>132.1</v>
+        <v>138.55</v>
       </c>
       <c r="I5" t="n">
         <v>138.1844352064822</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>6.13</v>
       </c>
       <c r="L5" t="n">
         <v>3.35</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.77</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44676.38541666666</v>
+        <v>44676.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>153.35</v>
+        <v>152.5</v>
       </c>
       <c r="I6" t="n">
         <v>152.7511350675323</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>10.68</v>
+        <v>10.07</v>
       </c>
       <c r="L6" t="n">
         <v>5.27</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>146.75</v>
+        <v>148</v>
       </c>
       <c r="I7" t="n">
         <v>147.5105519307947</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>3.77</v>
+        <v>2.95</v>
       </c>
       <c r="L7" t="n">
         <v>3.15</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.23</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44725.55208333334</v>
+        <v>44726.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>152.15</v>
+        <v>146.4</v>
       </c>
       <c r="I8" t="n">
         <v>149.7923946428721</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>-1.08</v>
       </c>
       <c r="L8" t="n">
         <v>3.95</v>
       </c>
       <c r="M8" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>1.74</v>
+        <v>5.09</v>
       </c>
       <c r="O8" t="n">
         <v>0.37</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>7.41</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>145.5</v>
+        <v>146.65</v>
       </c>
       <c r="I9" t="n">
         <v>145.9153650287048</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>0.61</v>
+        <v>-0.17</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="N9" t="n">
         <v>3.89</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.24</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>188.2</v>
+        <v>179.6</v>
       </c>
       <c r="I10" t="n">
         <v>185.0798037437451</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K10" t="n">
-        <v>28.33</v>
+        <v>22.47</v>
       </c>
       <c r="L10" t="n">
         <v>4.71</v>
@@ -1011,7 +1130,7 @@
         <v>6.77</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.49</v>
       </c>
       <c r="O10" t="n">
         <v>0.1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>189</v>
+        <v>193.6</v>
       </c>
       <c r="I11" t="n">
         <v>192.3483486147575</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.23</v>
+        <v>-7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>5.6</v>
+        <v>8.16</v>
       </c>
       <c r="M11" t="n">
         <v>2.17</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.67</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>274.7</v>
+        <v>259.25</v>
       </c>
       <c r="I12" t="n">
         <v>264.5775157267294</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>41.89</v>
+        <v>33.91</v>
       </c>
       <c r="L12" t="n">
         <v>5.86</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.44</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44907.55208333334</v>
+        <v>44908.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>257.35</v>
+        <v>278.3</v>
       </c>
       <c r="I13" t="n">
         <v>277.8320869316927</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.73</v>
+        <v>-7.35</v>
       </c>
       <c r="L13" t="n">
-        <v>6.23</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.44</v>
       </c>
       <c r="O13" t="n">
         <v>-7.92</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>12.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>267.15</v>
+        <v>246.2</v>
       </c>
       <c r="I14" t="n">
         <v>262.7045054889343</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.01</v>
+        <v>-11.53</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>11.62</v>
       </c>
       <c r="M14" t="n">
         <v>0.89</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>16.79</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>282.85</v>
+        <v>286.8</v>
       </c>
       <c r="I15" t="n">
         <v>284.3583609116037</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.89</v>
+        <v>-16.49</v>
       </c>
       <c r="L15" t="n">
-        <v>16.33</v>
+        <v>20.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.34</v>
+        <v>3.29</v>
       </c>
       <c r="N15" t="n">
         <v>4.64</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>272.8</v>
+        <v>263.2</v>
       </c>
       <c r="I16" t="n">
         <v>266.2557752423194</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.88</v>
+        <v>-8.23</v>
       </c>
       <c r="L16" t="n">
         <v>8.73</v>
@@ -1353,7 +1544,7 @@
         <v>0.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>3.57</v>
       </c>
       <c r="O16" t="n">
         <v>-1.45</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.46</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>262.25</v>
+        <v>278</v>
       </c>
       <c r="I17" t="n">
         <v>265.036664870191</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>0.36</v>
+        <v>-5.62</v>
       </c>
       <c r="L17" t="n">
-        <v>3.84</v>
+        <v>5.83</v>
       </c>
       <c r="M17" t="n">
         <v>0.57</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>5.85</v>
       </c>
       <c r="O17" t="n">
         <v>-3.57</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>10.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>268.3</v>
+        <v>250.6</v>
       </c>
       <c r="I18" t="n">
         <v>258.1260746638453</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.49</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>5.22</v>
+        <v>10.49</v>
       </c>
       <c r="M18" t="n">
         <v>0.89</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>7.58</v>
       </c>
       <c r="O18" t="n">
         <v>5.85</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>13.77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>269.4</v>
+        <v>274.95</v>
       </c>
       <c r="I19" t="n">
         <v>270.9806641529528</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.5</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>8.859999999999999</v>
+        <v>11.63</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.86</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>292.3</v>
+        <v>284.05</v>
       </c>
       <c r="I20" t="n">
         <v>285.1738980976219</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>6.31</v>
+        <v>3.31</v>
       </c>
       <c r="L20" t="n">
         <v>2.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>9.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>307.4</v>
+        <v>314.85</v>
       </c>
       <c r="I21" t="n">
         <v>310.0932254711017</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.220000000000001</v>
+        <v>-10.84</v>
       </c>
       <c r="L21" t="n">
-        <v>10.23</v>
+        <v>10.91</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8</v>
+        <v>1.79</v>
       </c>
       <c r="N21" t="n">
         <v>4.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>301.55</v>
+        <v>294.15</v>
       </c>
       <c r="I22" t="n">
         <v>300.9440178793576</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.22</v>
+        <v>-6.57</v>
       </c>
       <c r="L22" t="n">
-        <v>5.15</v>
+        <v>7.04</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>4.86</v>
+        <v>6.9</v>
       </c>
       <c r="O22" t="n">
         <v>2.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>263.25</v>
+        <v>269.35</v>
       </c>
       <c r="I23" t="n">
         <v>268.614293451708</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
-        <v>10.5</v>
+        <v>8.43</v>
       </c>
       <c r="L23" t="n">
         <v>4.3</v>
@@ -1752,7 +2027,7 @@
         <v>1.26</v>
       </c>
       <c r="N23" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
         <v>-6.9</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.56</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45168.38541666666</v>
+        <v>45168.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>371.15</v>
+        <v>364.55</v>
       </c>
       <c r="I24" t="n">
         <v>366.6654361370092</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>89</v>
+        <v>89.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>37.79</v>
+        <v>35.34</v>
       </c>
       <c r="L24" t="n">
         <v>2.39</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.84</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45184.55208333334</v>
+        <v>45187.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>378.1</v>
+        <v>393</v>
       </c>
       <c r="I25" t="n">
         <v>385.7987787706895</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.72</v>
+        <v>-7.8</v>
       </c>
       <c r="L25" t="n">
-        <v>7.24</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>0.74</v>
       </c>
       <c r="N25" t="n">
-        <v>3.01</v>
+        <v>4.03</v>
       </c>
       <c r="O25" t="n">
         <v>-2.6</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>390.4</v>
+        <v>385.55</v>
       </c>
       <c r="I26" t="n">
         <v>387.209575674074</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.66</v>
+        <v>-1.9</v>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="M26" t="n">
         <v>1.35</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.72</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45242.76041666666</v>
+        <v>45243.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>400.2</v>
+        <v>417.75</v>
       </c>
       <c r="I27" t="n">
         <v>413.3572580546554</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>17.375</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.8</v>
+        <v>-8.35</v>
       </c>
       <c r="L27" t="n">
         <v>8.68</v>
@@ -1980,7 +2303,7 @@
         <v>2.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.98</v>
+        <v>7.06</v>
       </c>
       <c r="O27" t="n">
         <v>-2.15</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45247.55208333334</v>
+        <v>45250.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>413.6</v>
+        <v>406.95</v>
       </c>
       <c r="I28" t="n">
         <v>407.0368997964512</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.99</v>
+        <v>-2.59</v>
       </c>
       <c r="L28" t="n">
         <v>4.7</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.49</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>401.4</v>
+        <v>407.4</v>
       </c>
       <c r="I29" t="n">
         <v>405.7803018142609</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>1.36</v>
+        <v>-0.11</v>
       </c>
       <c r="L29" t="n">
         <v>2</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.55208333334</v>
+        <v>45281.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>411.5</v>
+        <v>385.05</v>
       </c>
       <c r="I30" t="n">
         <v>400.132540533688</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>1.01</v>
+        <v>-5.49</v>
       </c>
       <c r="L30" t="n">
-        <v>2.61</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.36</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>3.48</v>
+        <v>4.12</v>
       </c>
       <c r="O30" t="n">
         <v>3.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>421.1</v>
+        <v>422.45</v>
       </c>
       <c r="I31" t="n">
         <v>422.2913395529561</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>10.09</v>
+        <v>10.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.02</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.74</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>508.65</v>
+        <v>480.95</v>
       </c>
       <c r="I32" t="n">
         <v>483.741483522312</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>20.4</v>
+        <v>13.85</v>
       </c>
       <c r="L32" t="n">
         <v>2.49</v>
@@ -2265,7 +2648,7 @@
         <v>1.33</v>
       </c>
       <c r="N32" t="n">
-        <v>3.49</v>
+        <v>6.65</v>
       </c>
       <c r="O32" t="n">
         <v>0.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.29</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>478.3</v>
+        <v>502.2</v>
       </c>
       <c r="I33" t="n">
         <v>496.119587153388</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K33" t="n">
-        <v>0.55</v>
+        <v>-4.42</v>
       </c>
       <c r="L33" t="n">
         <v>11.73</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.99</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>513.5</v>
+        <v>488.95</v>
       </c>
       <c r="I34" t="n">
         <v>493.5753947741917</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>2.25</v>
+        <v>-2.64</v>
       </c>
       <c r="L34" t="n">
         <v>4.88</v>
@@ -2379,7 +2786,7 @@
         <v>1.42</v>
       </c>
       <c r="N34" t="n">
-        <v>2.17</v>
+        <v>4.06</v>
       </c>
       <c r="O34" t="n">
         <v>4.2</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.39</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45433.38541666666</v>
+        <v>45433.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>523.6</v>
+        <v>547.25</v>
       </c>
       <c r="I35" t="n">
         <v>530.5621239835214</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.09</v>
+        <v>-11.92</v>
       </c>
       <c r="L35" t="n">
-        <v>7.2</v>
+        <v>13.25</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>579.35</v>
+        <v>484.85</v>
       </c>
       <c r="I36" t="n">
         <v>522.8920809593889</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>5.87</v>
+        <v>-11.4</v>
       </c>
       <c r="L36" t="n">
-        <v>4.38</v>
+        <v>15.37</v>
       </c>
       <c r="M36" t="n">
         <v>0.25</v>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>13.15</v>
       </c>
       <c r="O36" t="n">
         <v>6.45</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>24.87</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>526.2</v>
+        <v>529.85</v>
       </c>
       <c r="I37" t="n">
         <v>529.2958310271956</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.529999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L37" t="n">
         <v>19.33</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45509.55208333334</v>
+        <v>45510.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>549.25</v>
+        <v>540.35</v>
       </c>
       <c r="I38" t="n">
         <v>541.9214440838447</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.66</v>
+        <v>1.98</v>
       </c>
       <c r="L38" t="n">
         <v>1.99</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.98</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45558.38541666666</v>
+        <v>45558.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>507.2</v>
+        <v>509.5</v>
       </c>
       <c r="I39" t="n">
         <v>508.4998743502965</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>6.13</v>
+        <v>5.71</v>
       </c>
       <c r="L39" t="n">
         <v>3.96</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.39</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>490.75</v>
+        <v>481</v>
       </c>
       <c r="I40" t="n">
         <v>483.6704837846975</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.68</v>
+        <v>-5.59</v>
       </c>
       <c r="L40" t="n">
-        <v>4.92</v>
+        <v>6.22</v>
       </c>
       <c r="M40" t="n">
         <v>1.75</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45593.38541666666</v>
+        <v>45593.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>490.05</v>
+        <v>526.95</v>
       </c>
       <c r="I41" t="n">
         <v>502.5752449352252</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.88</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>2.42</v>
+        <v>11.26</v>
       </c>
       <c r="M41" t="n">
         <v>1.21</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45610.38541666666</v>
+        <v>45610.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>521.25</v>
+        <v>513.75</v>
       </c>
       <c r="I42" t="n">
         <v>515.7031965867752</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.08</v>
+        <v>-2.5</v>
       </c>
       <c r="L42" t="n">
         <v>7.59</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.74</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>508.35</v>
+        <v>535.6</v>
       </c>
       <c r="I43" t="n">
         <v>531.7922007862074</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>1.05</v>
+        <v>-4.25</v>
       </c>
       <c r="L43" t="n">
-        <v>1.57</v>
+        <v>11.13</v>
       </c>
       <c r="M43" t="n">
-        <v>0.48</v>
+        <v>1.23</v>
       </c>
       <c r="N43" t="n">
-        <v>1.07</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
         <v>-0.62</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.24</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>541.05</v>
+        <v>533.85</v>
       </c>
       <c r="I44" t="n">
         <v>536.1963451862115</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>1.02</v>
+        <v>-0.33</v>
       </c>
       <c r="L44" t="n">
         <v>3.92</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>480.4</v>
+        <v>503.8</v>
       </c>
       <c r="I45" t="n">
         <v>484.7071529584006</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K45" t="n">
-        <v>10.01</v>
+        <v>5.63</v>
       </c>
       <c r="L45" t="n">
         <v>1.56</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>484.9</v>
+        <v>479.15</v>
       </c>
       <c r="I46" t="n">
         <v>479.1603156536503</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.75</v>
+        <v>-4.89</v>
       </c>
       <c r="L46" t="n">
-        <v>4.68</v>
+        <v>5.61</v>
       </c>
       <c r="M46" t="n">
         <v>0.21</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.97</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45686.38541666666</v>
+        <v>45686.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>503.1</v>
+        <v>520.9</v>
       </c>
       <c r="I47" t="n">
         <v>504.6317607401684</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>-5</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>5.29</v>
+        <v>10.34</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>500.3</v>
+        <v>490.25</v>
       </c>
       <c r="I48" t="n">
         <v>490.6128518144878</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.95</v>
+        <v>-5.88</v>
       </c>
       <c r="L48" t="n">
         <v>6.25</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>501.2</v>
+        <v>508.45</v>
       </c>
       <c r="I49" t="n">
         <v>503.8976314717448</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.23</v>
+        <v>-3.71</v>
       </c>
       <c r="L49" t="n">
         <v>4.18</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.42</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>617.05</v>
+        <v>611.65</v>
       </c>
       <c r="I50" t="n">
         <v>613.7616742809331</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>112.1666666666667</v>
+        <v>113</v>
       </c>
       <c r="K50" t="n">
-        <v>21.36</v>
+        <v>20.3</v>
       </c>
       <c r="L50" t="n">
         <v>2.76</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.63</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45862.38541666666</v>
+        <v>45862.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>617.35</v>
+        <v>642.45</v>
       </c>
       <c r="I51" t="n">
         <v>634.3546338436712</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.93</v>
+        <v>-5.04</v>
       </c>
       <c r="L51" t="n">
-        <v>4.04</v>
+        <v>5.17</v>
       </c>
       <c r="M51" t="n">
         <v>0.49</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.42</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45982.38541666666</v>
+        <v>45982.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>843.65</v>
+        <v>835.9</v>
       </c>
       <c r="I52" t="n">
         <v>840.2196137838038</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>119.8333333333333</v>
+        <v>120</v>
       </c>
       <c r="K52" t="n">
-        <v>31.32</v>
+        <v>30.11</v>
       </c>
       <c r="L52" t="n">
         <v>7.64</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.55</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46021.38541666666</v>
+        <v>46021.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>785.45</v>
+        <v>790.25</v>
       </c>
       <c r="I53" t="n">
         <v>787.6311213948887</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>6.04</v>
+        <v>5.46</v>
       </c>
       <c r="L53" t="n">
         <v>4.53</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>810.25</v>
+        <v>796.85</v>
       </c>
       <c r="I54" t="n">
         <v>806.1907064036861</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>2.53</v>
+        <v>0.84</v>
       </c>
       <c r="L54" t="n">
         <v>0.83</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>841.35</v>
+        <v>884.3</v>
       </c>
       <c r="I55" t="n">
         <v>844.774318826329</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.58</v>
+        <v>-10.97</v>
       </c>
       <c r="L55" t="n">
-        <v>7.62</v>
+        <v>11.57</v>
       </c>
       <c r="M55" t="n">
         <v>0.78</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>857.4</v>
+        <v>824.45</v>
       </c>
       <c r="I56" t="n">
         <v>836.6126226617505</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.04</v>
+        <v>-6.77</v>
       </c>
       <c r="L56" t="n">
-        <v>7.07</v>
+        <v>7.68</v>
       </c>
       <c r="M56" t="n">
         <v>0.58</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.98</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>885.25</v>
+        <v>894.95</v>
       </c>
       <c r="I57" t="n">
         <v>890.0585682716255</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.37</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>8.140000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="M57" t="n">
         <v>4.2</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>954.15</v>
+        <v>907.55</v>
       </c>
       <c r="I58" t="n">
         <v>921.3417936745817</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>6.61</v>
+        <v>1.41</v>
       </c>
       <c r="L58" t="n">
         <v>5.57</v>
@@ -3747,7 +4442,7 @@
         <v>2.73</v>
       </c>
       <c r="N58" t="n">
-        <v>1.61</v>
+        <v>3.34</v>
       </c>
       <c r="O58" t="n">
         <v>0.43</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>854.8</v>
+        <v>894.5</v>
       </c>
       <c r="I59" t="n">
         <v>889.7522796074114</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>5.81</v>
+        <v>1.44</v>
       </c>
       <c r="L59" t="n">
         <v>3.72</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.83</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>894.95</v>
+        <v>878.05</v>
       </c>
       <c r="I60" t="n">
         <v>878.1370677110106</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>0.05</v>
+        <v>-1.84</v>
       </c>
       <c r="L60" t="n">
         <v>8.6</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.61</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>822.5</v>
+        <v>849.3</v>
       </c>
       <c r="I61" t="n">
         <v>837.2973091711812</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K61" t="n">
-        <v>6.33</v>
+        <v>3.27</v>
       </c>
       <c r="L61" t="n">
         <v>3.22</v>
@@ -3918,7 +4649,7 @@
         <v>1.81</v>
       </c>
       <c r="N61" t="n">
-        <v>2.79</v>
+        <v>4.4</v>
       </c>
       <c r="O61" t="n">
         <v>-1.84</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.33</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46197.55208333334</v>
+        <v>46198.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>842.25</v>
+        <v>836</v>
       </c>
       <c r="I62" t="n">
         <v>837.0706875536562</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.83</v>
+        <v>-1.57</v>
       </c>
       <c r="L62" t="n">
         <v>3.75</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.22</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>793.4</v>
+        <v>855.75</v>
       </c>
       <c r="I63" t="n">
         <v>825.8557402715367</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>5.1</v>
+        <v>-2.36</v>
       </c>
       <c r="L63" t="n">
-        <v>1.79</v>
+        <v>4.36</v>
       </c>
       <c r="M63" t="n">
         <v>0.91</v>
       </c>
       <c r="N63" t="n">
-        <v>2.31</v>
+        <v>10.08</v>
       </c>
       <c r="O63" t="n">
         <v>-1.1</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.9</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46274.38541666666</v>
+        <v>46274.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>856.55</v>
+        <v>851.05</v>
       </c>
       <c r="I64" t="n">
         <v>856.1585214122535</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>0.09</v>
+        <v>-0.55</v>
       </c>
       <c r="L64" t="n">
         <v>7.13</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>818.9</v>
+        <v>832.85</v>
       </c>
       <c r="I65" t="n">
         <v>826.7547799600592</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>3.78</v>
+        <v>2.14</v>
       </c>
       <c r="L65" t="n">
         <v>2.21</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>20</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.9</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.96</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.75</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.89</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.39</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.7</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.33</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.5</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
